--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supneta_a_2019.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supneta_a_2019.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:54</t>
+    <t xml:space="preserve">2026-09-24 00:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -603,7 +603,7 @@
         <v>-0.24</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -614,10 +614,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.38</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -628,10 +628,10 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11">
@@ -642,10 +642,10 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12">
@@ -670,10 +670,10 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.13</v>
+        <v>0.07</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14">
@@ -684,10 +684,10 @@
         <v>19</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15">
@@ -701,7 +701,7 @@
         <v>0.21</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supneta_a_2019.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supneta_a_2019.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:45</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supneta_a_2019.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_e_supneta_a_2019.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
